--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2340,6 +2340,411 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>网站地图</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/jyb_sy/s3636/202610/t20261020_1455285.html</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>教育部中央文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>教育部办公厅&amp;nbsp;&amp;nbsp;国家卫生健康委办公厅&amp;nbsp;&amp;nbsp;国家疾控局综合司关于防控儿童青少年高度近视的...</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/srcsite/A17/moe_943/s3285/202610/t20261020_1455236.html</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>教育部-站内搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>国务院学位委员会关于下达2026年度学位授予资格自主审核单位撤销和增设学位授予点名单...</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/srcsite/A22/yjss_xwgl/moe_818/202610/t20261020_1455259.html</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>教育部-站内搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>国务院学位委员会关于下达2025年度学位授予资格自主审核单位撤销和增设学位授予点名单...</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/srcsite/A22/yjss_xwgl/moe_818/202610/t20261020_1455255.html</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>教育部-站内搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>国务院学位委员会关于下达2026年度动态调整撤销和增设学位授予点名单的通知</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/srcsite/A22/yjss_xwgl/moe_818/202610/t20261020_1455250.html</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>教育部-站内搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>国务院学位委员会关于下达2025年度动态调整撤销和增设学位授予点名单的通知</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/srcsite/A22/yjss_xwgl/moe_818/202610/t20261020_1455230.html</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>教育部-站内搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于2026年第四十一批一级建造师注册人员名单的公告</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_b53b69c8f1bc43d98b71782130dd379a.html</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于印发《历史文化名城（镇、村）与历史建筑保护传承“十五五”规划》的通知</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_20b973138dab4ccb9c556cedb78b37ae.html</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>关于汕尾市海丰县人民检察院“两房”迁建项目可行性研究报告的批复</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4968/post_4968414.html</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>关于佛山市三水区人民检察院办案和专业技术用房建设项目建议书的批复</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4968/post_4968416.html</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>关于广东科贸职业学院清远校区新建综合楼、实训楼、教学楼项目初步设计概算的批复</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4968/post_4968418.html</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于转下达2026年节能减排补助资金预算（第三批）的通知</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4968/post_4968510.html</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于开展广东省建筑施工特种作业操作资格证书换发工作的通知</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4968/post_4968528.html</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于暂扣广东茂亿建设工程有限公司等7家建筑施工企业安全生产许可证行政处罚意见告知书的送达公告</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4968/post_4968508.html</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>新疆发改委监测调度中央预算内投资项目,2026年项目开工率达90%</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>http://news.10jqka.com.cn/20261019/c680811512.shtml</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>同花顺</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2745,6 +2745,195 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>国务院</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>中办国办关于推动科技创新和产业创新深度融合的意见</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.gov.cn/zhengce/202610/content_7083930.htm</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>国务院-最新政策</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>教育部办公厅关于2026年度教育部哲学社会科学研究重大课题攻关项目和高校思政课教师研...</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/srcsite/A13/moe_2557/moe_2558/202610/t20261021_1455439.html</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>教育部-站内搜索</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026年度全省海洋产业高质量发展推进工作会议召开 奋发进取 积极作为 加快构建具有广东特色广东优势的现代化海洋产业体系 孟凡利出席并讲话</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4969/post_4969196.html</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>广东十个项目入选首批国家标志性重大应用场景项目</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4968/post_4968963.html</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>广东九个案例入选国家首批要素市场化配置综合改革试点创新举措</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4968/post_4968988.html</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>宁夏监管局:加强财政科学管理 推动超长期特别国债 消费品以旧换新...</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>http://news.10jqka.com.cn/20261020/c680893406.shtml</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>同花顺</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>国家发改委:用好超长期特别国债资金 加快新型政策性金融工具资金...</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.zhitongcaijing.com/content/detail/1509275.html</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>智通财经</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2934,6 +2934,276 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>国家发展改革委有关负责同志就《对外投资管理办法》答记者问</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn/xxgk/jd/jd/202610/t20261022_1408302.html</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>发改委-文件库</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>《对外投资管理办法》 2026年第49号令</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn/xxgk/zcfb/fzggwl/202610/t20261022_1408298.html</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>发改委-文件库</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>对外投资管理办法</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://zfxxgk.ndrc.gov.cn/web/dirlist.jsp/iteminfo.jsp?id=20667</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>发改委-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>教育部</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>中共中央办公厅 国务院办公厅关于推动科技创新和产业创新深度融合的意见</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>http://www.moe.gov.cn/jyb_xxgk/moe_1777/moe_1778/202610/t20261022_1455553.html</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>教育部中央文件</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>关于广东技术师范大学白云校区新建研究生公寓项目可行性研究报告的批复</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4969/post_4969387.html</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于2026年广东省政府专项债券（四十五期～四十七期）发行有关事宜的通知</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4969/post_4969467.html</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于2026年广东省地方政府再融资一般债券（五期）发行有关事宜的通知</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4969/post_4969464.html</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于2026年广东省政府一般债券（九期）和专项债券（四十八期）发行有关事宜的通知</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4969/post_4969460.html</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>机构:超长期特别国债发行完毕,政策资金供给持续增强</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>http://news.10jqka.com.cn/20261021/c680921468.shtml</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>同花顺</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>...聚焦国际科技创新中心三大核心功能建设,争取超长期特别国债等支持</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.yicai.com/news/103401838.html</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>第一财经</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -1953,7 +1953,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://zfxxgk.ndrc.gov.cn/web/dirlist.jsp/iteminfo.jsp?id=20665</t>
+          <t>https://zfxxgk.ndrc.gov.cn/web/iteminfo.jsp?id=20665</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://zfxxgk.ndrc.gov.cn/web/dirlist.jsp/iteminfo.jsp?id=20667</t>
+          <t>https://zfxxgk.ndrc.gov.cn/web/iteminfo.jsp?id=20667</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2942,22 +2942,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>发改委</t>
+          <t>财政部</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>国家发展改革委有关负责同志就《对外投资管理办法》答记者问</t>
+          <t>2026年大中型水库移民后期扶持资金分配结果</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.ndrc.gov.cn/xxgk/jd/jd/202610/t20261022_1408302.html</t>
+          <t>http://nys.mof.gov.cn/zxzyzf/dzxskymhqfczj/202610/t20261023_4003344.htm</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>发改委-文件库</t>
+          <t>专项资金-大中型水库移民后期扶持资金</t>
         </is>
       </c>
     </row>
@@ -2969,22 +2969,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>发改委</t>
+          <t>住建部</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>《对外投资管理办法》 2026年第49号令</t>
+          <t>住房城乡建设部办公厅等关于推进老旧街区厂区改造提升的指导意见</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.ndrc.gov.cn/xxgk/zcfb/fzggwl/202610/t20261022_1408298.html</t>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_4e701b22880944b38799ca132532dfbd.html</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>发改委-文件库</t>
+          <t>住建部-政策库</t>
         </is>
       </c>
     </row>
@@ -2996,22 +2996,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>发改委</t>
+          <t>新闻栏目</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>对外投资管理办法</t>
+          <t>机构:超长期特别国债发行完毕,政策资金供给持续增强</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://zfxxgk.ndrc.gov.cn/web/iteminfo.jsp?id=20667</t>
+          <t>http://news.10jqka.com.cn/20261021/c680921468.shtml</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>发改委-信息公开</t>
+          <t>同花顺</t>
         </is>
       </c>
     </row>
@@ -3023,182 +3023,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>教育部</t>
+          <t>新闻栏目</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>中共中央办公厅 国务院办公厅关于推动科技创新和产业创新深度融合的意见</t>
+          <t>...聚焦国际科技创新中心三大核心功能建设,争取超长期特别国债等支持</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>http://www.moe.gov.cn/jyb_xxgk/moe_1777/moe_1778/202610/t20261022_1455553.html</t>
+          <t>https://www.yicai.com/news/103401838.html</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
-        <is>
-          <t>教育部中央文件</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>广东省发改委</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>关于广东技术师范大学白云校区新建研究生公寓项目可行性研究报告的批复</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4969/post_4969387.html</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>广东-政务公开</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>广东省财政厅</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>广东省财政厅关于2026年广东省政府专项债券（四十五期～四十七期）发行有关事宜的通知</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4969/post_4969467.html</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>广东财政厅-信息公开</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>广东省财政厅</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>广东省财政厅关于2026年广东省地方政府再融资一般债券（五期）发行有关事宜的通知</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4969/post_4969464.html</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>广东财政厅-信息公开</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>广东省财政厅</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>广东省财政厅关于2026年广东省政府一般债券（九期）和专项债券（四十八期）发行有关事宜的通知</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4969/post_4969460.html</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>广东财政厅-信息公开</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>新闻栏目</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>机构:超长期特别国债发行完毕,政策资金供给持续增强</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>http://news.10jqka.com.cn/20261021/c680921468.shtml</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>同花顺</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>新闻栏目</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>...聚焦国际科技创新中心三大核心功能建设,争取超长期特别国债等支持</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://www.yicai.com/news/103401838.html</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
         <is>
           <t>第一财经</t>
         </is>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3042,6 +3042,438 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>国务院</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>国办关于适应人工智能技术发展助力构建就业友好型发展方式的意见</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.gov.cn/zhengce/content/202610/content_7084107.htm</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>国务院-最新政策</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>国家发展改革委印发《能源保供中长期合同管理办法（试行）》</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn/xxgk/jd/jd/202610/t20261023_1408367.html</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>发改委-文件库</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>国家发展改革委有关负责同志就《能源保供中长期合同管理办法（试行）》答记者问</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn/xxgk/jd/jd/202610/t20261023_1408366.html</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>发改委-文件库</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>《能源保供中长期合同管理办法(试行)》 2026年第50号令</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn/xxgk/zcfb/fzggwl/202610/t20261023_1408364.html</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>发改委-文件库</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>关于公布2027—2028年小麦最低收购价格的通知(发改价格〔2026〕1527号)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://zfxxgk.ndrc.gov.cn/web/iteminfo.jsp?id=20669</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>发改委-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>能源保供中长期合同管理办法（试行）</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://zfxxgk.ndrc.gov.cn/web/iteminfo.jsp?id=20668</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>发改委-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于核准2026年度第十批建设工程企业资质延续名单的公告</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_a4164ea3440147368375b6fb8f29ae29.html</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于核准2026年度第十批建设工程企业资质名单的公告</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_3b973cab21e740cfaf4d55ef1e84f5af.html</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>关于广东省中学实验仪器设备购置项目初步设计概算的批复</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4969/post_4969717.html</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于佛山市盈正房地产土地评估有限公司等4家机构的注销备案公告</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4970/post_4970147.html</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于广东中毅资产土地房地产评估有限公司云浮分公司等2家机构的备案公告</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4970/post_4970145.html</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于征求广东省工程建设标准《城市道路隧道设计标准（送审稿）》意见的公告</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4970/post_4970087.html</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>国家发展改革委紧急安排3000万元中央预算内投资 支持灾区基础设施...</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://finance.eastmoney.com/a/202610233905846983.html</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>东方财富网</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>国家发展改革委紧急安排3000万元中央预算内投资支持西藏巴青7.0级...</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com/gn/2026/10-23/10719625.shtml</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>中国新闻网</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>财政部辽宁监管局:多措并举 加力提升 消费品以旧换新重点绩效评价...</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>http://news.10jqka.com.cn/20261023/c681015237.shtml</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>同花顺</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>山东省开展超长期特别国债政策落实和资金管理使用情况专项审计调查</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>https://v.iqilu.com/sdws/sdxwlb/2026/1023/5957583.html</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>齐鲁网</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3474,6 +3474,195 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>国务院</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>事业单位登记管理条例</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>https://www.gov.cn/zhengce/content/202610/content_7084279.htm</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>国务院-最新政策</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于公布2026年全国“十佳环卫人”名单的通知</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_94604fbcdde44fdeb14b3023bf34359f.html</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于2026年第十九批注册监理工程师初始注册人员名单的公告</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_2e2dc5e6b212465395c7a726424c189d.html</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于2026年广东省政府债券四季度发行计划的公告</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4970/post_4970830.html</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于广州地铁设计院施工图咨询有限公司等四家施工图审查机构评审意见的公示</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4971/post_4971039.html</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>广东省河源市龙川县佗城等5个历史文化名城、名村保护规划获省政府批复</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4970/post_4970882.html</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>致全省环卫工人的慰问信</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4970/post_4970840.html</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3663,6 +3663,303 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>财政部</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>关于下达2026年城乡义务教育补助经费（第二批）预算的通知</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>http://jkw.mof.gov.cn/ybxzyzf/cxywjybzjf/202610/t20261027_4003581.htm</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>专项资金-城乡义务教育补助经费</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>财政部</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>关于下达2026年义务教育薄弱环节改善与能力提升补助资金预算的通知</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>http://jkw.mof.gov.cn/zxzyzf/ncywjybrxxgzbzzj/202610/t20261027_4003585.htm</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>专项资金-农村义务教育薄弱学校改造补助资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>财政部</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>关于印发《义务教育薄弱环节改善与能力提升补助资金管理办法》的通知</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>http://jkw.mof.gov.cn/zxzyzf/ncywjybrxxgzbzzj/202610/t20261027_4003586.htm</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>专项资金-农村义务教育薄弱学校改造补助资金</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于2026年第二十三批一级造价工程师初始注册人员名单的公告</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_99431b9a7f62419bb575da132ab54b3d.html</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>关于广东省第三荣军优抚医院新建医技综合大楼项目初步设计概算的批复</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4971/post_4971239.html</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>中国共产党广东省发展和改革委员会直属机关第五次代表大会胜利召开</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4970/post_4970651.html</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>关于广东外语外贸大学白云山校区新建学生宿舍项目可行性研究报告的批复</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4971/post_4971099.html</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>关于广东技术师范大学白云校区新建学生宿舍项目可行性研究报告的批复</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4971/post_4971104.html</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于广东省地方标准《大型公共建筑钢结构安全运维技术标准》的通告</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4971/post_4971567.html</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>发挥超长期特别国债资金效益</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://guancha.gmw.cn/2026-10/26/content_39064892.htm</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>光明网</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>【财金视野】发挥超长期特别国债资金效益</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.chinanews.com/cj/2026/10-26/10721040.shtml</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>中国新闻网</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3960,6 +3960,195 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>发改委</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>关于同意南方区域电力市场转入正式运行的复函(发改办体改〔2026〕715号)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://www.ndrc.gov.cn/xxgk/zcfb/tz/202610/t20261028_1408423.html</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>发改委-政策发布通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>广东省发改委</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>关于韶关学院韶乐园本科生宿舍项目初步设计概算的批复</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://drc.gd.gov.cn/gkmlpt/content/4/4971/post_4971959.html</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>广东-政务公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于广东志诚房地产土地资产评估有限公司变更备案的公告</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4972/post_4972037.html</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>广东省财政厅</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>广东省财政厅关于开展广东省第六期高端会计人才选拔培养工作的通知</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://czt.gd.gov.cn/gkmlpt/content/4/4971/post_4971876.html</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>广东财政厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于征求广东省工程建设标准《污水处理厂设备更新标准（送审稿）》意见的公告</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4971/post_4971919.html</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于征求广东省地方标准《建筑共用用水系统设计施工验收标准（送审稿）》意见的公告</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4971/post_4971812.html</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>广东省住房和城乡建设厅关于征求《建筑施工现场高处作业平台（车）安全技术标准（征求意见稿）》意见的函</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4971/post_4971832.html</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_log.xlsx
+++ b/daily_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4149,6 +4149,114 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>关于2026年第二十批申请勘察设计注册工程师初始注册审查意见的公示</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_1b879630158b491ca6e20fbfa0b18e5d.html</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>住建部</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>住房城乡建设部关于2026年第十八批勘察设计注册工程师初始注册人员名单的公告</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.mohurd.gov.cn/gongkai/zc/wjk/art/2026/art_f7f8458f92224245a24f98c2ee3d5258.html</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>住建部-政策库</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>广东省住建厅</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>淘汰竹木脚手架 安全建房护万家</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>http://zfcxjst.gd.gov.cn/gkmlpt/content/4/4972/post_4972673.html</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>广东住建厅-信息公开</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>新闻栏目</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>山东监管局抓实&amp;quot;三个注重&amp;quot;,提升超长期特别国债资金使用质效</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>http://news.10jqka.com.cn/20261028/c681202273.shtml</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>同花顺</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
